--- a/onsenin_list.xlsx
+++ b/onsenin_list.xlsx
@@ -317,7 +317,7 @@
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1428750" cy="2219325"/>
+    <ext cx="1428750" cy="2228850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -342,7 +342,7 @@
       <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1428750" cy="2143125"/>
+    <ext cx="1428750" cy="2219325"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -367,7 +367,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1428750" cy="2228850"/>
+    <ext cx="1428750" cy="2143125"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -1260,6 +1260,531 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="2124075"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="45" name="Image 45" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId45"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>46</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1924050"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="46" name="Image 46" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId46"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>47</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="2133600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="47" name="Image 47" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId47"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>48</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="2114550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="48" name="Image 48" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId48"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>49</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="2143125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="49" name="Image 49" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId49"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>50</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="2162175"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="50" name="Image 50" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId50"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>51</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="2181225"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="51" name="Image 51" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId51"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>52</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="2133600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="52" name="Image 52" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId52"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>53</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="2133600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="53" name="Image 53" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId53"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>55</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="2124075"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="54" name="Image 54" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId54"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>56</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="2124075"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="55" name="Image 55" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId55"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>57</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="2095500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="56" name="Image 56" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId56"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>61</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="2133600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="57" name="Image 57" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId57"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>62</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="2143125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="58" name="Image 58" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId58"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>63</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="2152650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="59" name="Image 59" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId59"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>64</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="2133600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="60" name="Image 60" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId60"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>65</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="2124075"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="61" name="Image 61" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId61"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>66</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="2124075"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="62" name="Image 62" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId62"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="2085975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="63" name="Image 63" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId63"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>68</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="2114550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="64" name="Image 64" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId64"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>69</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="2162175"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="65" name="Image 65" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId65"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -1607,7 +2132,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>発売中・終了</t>
+          <t>発売状況</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -1915,7 +2440,7 @@
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
     </row>
-    <row r="8" ht="178.75" customHeight="1">
+    <row r="8" ht="179.5" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>宮城</t>
@@ -1943,7 +2468,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>リスVer</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr"/>
@@ -1952,16 +2477,16 @@
           <t>発売中</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2023-01-01</t>
-        </is>
-      </c>
+      <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>◯</t>
+        </is>
+      </c>
       <c r="L8" s="2" t="inlineStr"/>
     </row>
-    <row r="9" ht="172.75" customHeight="1">
+    <row r="9" ht="178.75" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>宮城</t>
@@ -1989,29 +2514,25 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>ブルーインパルス</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>終了</t>
+          <t>発売中</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2023-07-12</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>2024-11-21</t>
-        </is>
-      </c>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
     </row>
-    <row r="10" ht="179.5" customHeight="1">
+    <row r="10" ht="172.75" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>宮城</t>
@@ -2039,22 +2560,26 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>リスVer</t>
+          <t>ブルーインパルス</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>発売中</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>◯</t>
-        </is>
-      </c>
+          <t>終了</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2023-07-12</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
     </row>
     <row r="11" ht="172.75" customHeight="1">
@@ -3647,7 +4172,7 @@
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr"/>
     </row>
-    <row r="46" ht="24" customHeight="1">
+    <row r="46" ht="171.25" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
           <t>山形</t>
@@ -3693,7 +4218,7 @@
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr"/>
     </row>
-    <row r="47" ht="24" customHeight="1">
+    <row r="47" ht="155.5" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
           <t>山形</t>
@@ -3739,7 +4264,7 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr"/>
     </row>
-    <row r="48" ht="24" customHeight="1">
+    <row r="48" ht="172" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
           <t>山形</t>
@@ -3785,7 +4310,7 @@
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr"/>
     </row>
-    <row r="49" ht="24" customHeight="1">
+    <row r="49" ht="170.5" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
           <t>山形</t>
@@ -3831,7 +4356,7 @@
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr"/>
     </row>
-    <row r="50" ht="24" customHeight="1">
+    <row r="50" ht="172.75" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
           <t>山形</t>
@@ -3877,7 +4402,7 @@
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr"/>
     </row>
-    <row r="51" ht="24" customHeight="1">
+    <row r="51" ht="174.25" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
           <t>山形</t>
@@ -3923,7 +4448,7 @@
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr"/>
     </row>
-    <row r="52" ht="24" customHeight="1">
+    <row r="52" ht="175.75" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
           <t>山形</t>
@@ -3969,7 +4494,7 @@
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr"/>
     </row>
-    <row r="53" ht="24" customHeight="1">
+    <row r="53" ht="172" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
           <t>山形</t>
@@ -4015,7 +4540,7 @@
       </c>
       <c r="L53" s="2" t="inlineStr"/>
     </row>
-    <row r="54" ht="24" customHeight="1">
+    <row r="54" ht="172" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
           <t>山形</t>
@@ -4099,7 +4624,7 @@
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr"/>
     </row>
-    <row r="56" ht="24" customHeight="1">
+    <row r="56" ht="171.25" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
           <t>山形</t>
@@ -4145,7 +4670,7 @@
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
     </row>
-    <row r="57" ht="24" customHeight="1">
+    <row r="57" ht="171.25" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
           <t>山形</t>
@@ -4187,7 +4712,7 @@
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr"/>
     </row>
-    <row r="58" ht="24" customHeight="1">
+    <row r="58" ht="169" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
           <t>山形</t>
@@ -4379,7 +4904,7 @@
       </c>
       <c r="L61" s="2" t="inlineStr"/>
     </row>
-    <row r="62" ht="24" customHeight="1">
+    <row r="62" ht="172" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
           <t>山形</t>
@@ -4425,7 +4950,7 @@
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr"/>
     </row>
-    <row r="63" ht="24" customHeight="1">
+    <row r="63" ht="172.75" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
           <t>山形</t>
@@ -4471,7 +4996,7 @@
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr"/>
     </row>
-    <row r="64" ht="24" customHeight="1">
+    <row r="64" ht="173.5" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
           <t>山形</t>
@@ -4517,7 +5042,7 @@
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr"/>
     </row>
-    <row r="65" ht="24" customHeight="1">
+    <row r="65" ht="172" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
           <t>山形</t>
@@ -4567,7 +5092,7 @@
       </c>
       <c r="L65" s="2" t="inlineStr"/>
     </row>
-    <row r="66" ht="24" customHeight="1">
+    <row r="66" ht="171.25" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
           <t>山形</t>
@@ -4609,7 +5134,7 @@
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr"/>
     </row>
-    <row r="67" ht="24" customHeight="1">
+    <row r="67" ht="171.25" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
           <t>山形</t>
@@ -4651,7 +5176,7 @@
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr"/>
     </row>
-    <row r="68" ht="24" customHeight="1">
+    <row r="68" ht="168.25" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
           <t>山形</t>
@@ -4693,7 +5218,7 @@
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr"/>
     </row>
-    <row r="69" ht="24" customHeight="1">
+    <row r="69" ht="170.5" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
           <t>山形</t>
@@ -4739,7 +5264,7 @@
       </c>
       <c r="L69" s="2" t="inlineStr"/>
     </row>
-    <row r="70" ht="24" customHeight="1">
+    <row r="70" ht="174.25" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
           <t>山形</t>
@@ -6835,7 +7360,7 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>全身Ver</t>
+          <t>SDVer</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr"/>
@@ -6844,12 +7369,12 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="I118" s="2" t="inlineStr">
-        <is>
-          <t>2023-02-01</t>
-        </is>
-      </c>
-      <c r="J118" s="2" t="inlineStr"/>
+      <c r="I118" s="2" t="inlineStr"/>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>2024-02-11</t>
+        </is>
+      </c>
       <c r="K118" s="2" t="inlineStr"/>
       <c r="L118" s="2" t="inlineStr"/>
     </row>
@@ -6881,7 +7406,7 @@
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>SDVer</t>
+          <t>全身Ver</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr"/>
@@ -6890,12 +7415,12 @@
           <t>終了</t>
         </is>
       </c>
-      <c r="I119" s="2" t="inlineStr"/>
-      <c r="J119" s="2" t="inlineStr">
-        <is>
-          <t>2024-02-11</t>
-        </is>
-      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>2023-02-01</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr"/>
       <c r="K119" s="2" t="inlineStr"/>
       <c r="L119" s="2" t="inlineStr"/>
     </row>
@@ -10583,25 +11108,17 @@
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>おにぎり</t>
+          <t>旅</t>
         </is>
       </c>
       <c r="G202" s="3" t="inlineStr"/>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="I202" s="2" t="inlineStr">
-        <is>
-          <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="J202" s="2" t="inlineStr">
-        <is>
-          <t>2024-03-31</t>
-        </is>
-      </c>
+          <t>発売中</t>
+        </is>
+      </c>
+      <c r="I202" s="2" t="inlineStr"/>
+      <c r="J202" s="2" t="inlineStr"/>
       <c r="K202" s="2" t="inlineStr"/>
       <c r="L202" s="2" t="inlineStr"/>
     </row>
@@ -10633,17 +11150,25 @@
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t>旅</t>
+          <t>おにぎり</t>
         </is>
       </c>
       <c r="G203" s="3" t="inlineStr"/>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t>発売中</t>
-        </is>
-      </c>
-      <c r="I203" s="2" t="inlineStr"/>
-      <c r="J203" s="2" t="inlineStr"/>
+          <t>終了</t>
+        </is>
+      </c>
+      <c r="I203" s="2" t="inlineStr">
+        <is>
+          <t>2023-03-03</t>
+        </is>
+      </c>
+      <c r="J203" s="2" t="inlineStr">
+        <is>
+          <t>2024-03-31</t>
+        </is>
+      </c>
       <c r="K203" s="2" t="inlineStr"/>
       <c r="L203" s="2" t="inlineStr"/>
     </row>
@@ -11077,7 +11602,7 @@
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>立ち絵23春</t>
+          <t>法被SD</t>
         </is>
       </c>
       <c r="G213" s="3" t="inlineStr"/>
@@ -11088,10 +11613,14 @@
       </c>
       <c r="I213" s="2" t="inlineStr">
         <is>
-          <t>2023-04-15</t>
-        </is>
-      </c>
-      <c r="J213" s="2" t="inlineStr"/>
+          <t>2023-03-12</t>
+        </is>
+      </c>
+      <c r="J213" s="2" t="inlineStr">
+        <is>
+          <t>2024-03-31</t>
+        </is>
+      </c>
       <c r="K213" s="2" t="inlineStr"/>
       <c r="L213" s="2" t="inlineStr"/>
     </row>
@@ -11119,7 +11648,7 @@
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>立ち絵23夏</t>
+          <t>立ち絵23春</t>
         </is>
       </c>
       <c r="G214" s="3" t="inlineStr"/>
@@ -11130,7 +11659,7 @@
       </c>
       <c r="I214" s="2" t="inlineStr">
         <is>
-          <t>2023-06-24</t>
+          <t>2023-04-15</t>
         </is>
       </c>
       <c r="J214" s="2" t="inlineStr"/>
@@ -11161,7 +11690,7 @@
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>立ち絵秋</t>
+          <t>見返り美人</t>
         </is>
       </c>
       <c r="G215" s="3" t="inlineStr"/>
@@ -11172,7 +11701,7 @@
       </c>
       <c r="I215" s="2" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2023-05-20</t>
         </is>
       </c>
       <c r="J215" s="2" t="inlineStr"/>
@@ -11203,7 +11732,7 @@
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>立ち絵冬</t>
+          <t>立ち絵23夏</t>
         </is>
       </c>
       <c r="G216" s="3" t="inlineStr"/>
@@ -11214,14 +11743,10 @@
       </c>
       <c r="I216" s="2" t="inlineStr">
         <is>
-          <t>2023-12-09</t>
-        </is>
-      </c>
-      <c r="J216" s="2" t="inlineStr">
-        <is>
-          <t>2024-02-29</t>
-        </is>
-      </c>
+          <t>2023-06-24</t>
+        </is>
+      </c>
+      <c r="J216" s="2" t="inlineStr"/>
       <c r="K216" s="2" t="inlineStr"/>
       <c r="L216" s="2" t="inlineStr"/>
     </row>
@@ -11249,7 +11774,7 @@
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
-          <t>法被SD</t>
+          <t>立ち絵秋</t>
         </is>
       </c>
       <c r="G217" s="3" t="inlineStr"/>
@@ -11260,14 +11785,10 @@
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>2023-03-12</t>
-        </is>
-      </c>
-      <c r="J217" s="2" t="inlineStr">
-        <is>
-          <t>2024-03-31</t>
-        </is>
-      </c>
+          <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="J217" s="2" t="inlineStr"/>
       <c r="K217" s="2" t="inlineStr"/>
       <c r="L217" s="2" t="inlineStr"/>
     </row>
@@ -11295,7 +11816,7 @@
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>見返り美人</t>
+          <t>魚野の湯</t>
         </is>
       </c>
       <c r="G218" s="3" t="inlineStr"/>
@@ -11306,10 +11827,14 @@
       </c>
       <c r="I218" s="2" t="inlineStr">
         <is>
-          <t>2023-05-20</t>
-        </is>
-      </c>
-      <c r="J218" s="2" t="inlineStr"/>
+          <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="J218" s="2" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
       <c r="K218" s="2" t="inlineStr"/>
       <c r="L218" s="2" t="inlineStr"/>
     </row>
@@ -11337,7 +11862,7 @@
       </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
-          <t>魚野の湯</t>
+          <t>立ち絵冬</t>
         </is>
       </c>
       <c r="G219" s="3" t="inlineStr"/>
@@ -11348,12 +11873,12 @@
       </c>
       <c r="I219" s="2" t="inlineStr">
         <is>
-          <t>2023-11-11</t>
+          <t>2023-12-09</t>
         </is>
       </c>
       <c r="J219" s="2" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="K219" s="2" t="inlineStr"/>
@@ -11383,25 +11908,21 @@
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>立ち絵24春</t>
+          <t>立ち絵制服ver</t>
         </is>
       </c>
       <c r="G220" s="3" t="inlineStr"/>
       <c r="H220" s="2" t="inlineStr">
         <is>
-          <t>終了</t>
+          <t>発売中</t>
         </is>
       </c>
       <c r="I220" s="2" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="J220" s="2" t="inlineStr">
-        <is>
-          <t>2024-06-08</t>
-        </is>
-      </c>
+          <t>2024-02-03</t>
+        </is>
+      </c>
+      <c r="J220" s="2" t="inlineStr"/>
       <c r="K220" s="2" t="inlineStr"/>
       <c r="L220" s="2" t="inlineStr"/>
     </row>
@@ -11429,21 +11950,25 @@
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>立ち絵制服ver</t>
+          <t>立ち絵24春</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr"/>
       <c r="H221" s="2" t="inlineStr">
         <is>
-          <t>発売中</t>
+          <t>終了</t>
         </is>
       </c>
       <c r="I221" s="2" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
-        </is>
-      </c>
-      <c r="J221" s="2" t="inlineStr"/>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="J221" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-08</t>
+        </is>
+      </c>
       <c r="K221" s="2" t="inlineStr"/>
       <c r="L221" s="2" t="inlineStr"/>
     </row>
@@ -13724,18 +14249,18 @@
       </c>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>あいそめの湯</t>
+          <t>しゅうぷろ</t>
         </is>
       </c>
       <c r="D272" s="3" t="inlineStr"/>
       <c r="E272" s="3" t="inlineStr">
         <is>
-          <t>長野県上田市別所温泉58</t>
+          <t>長野県上田市別所温泉１６６１</t>
         </is>
       </c>
       <c r="F272" s="3" t="inlineStr">
         <is>
-          <t>紺浴衣Ver</t>
+          <t>芸姑</t>
         </is>
       </c>
       <c r="G272" s="3" t="inlineStr"/>
@@ -13746,7 +14271,7 @@
       </c>
       <c r="I272" s="2" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="J272" s="2" t="inlineStr"/>
@@ -13766,18 +14291,18 @@
       </c>
       <c r="C273" s="3" t="inlineStr">
         <is>
-          <t>別所温泉駅観光案内所</t>
+          <t>あいそめの湯</t>
         </is>
       </c>
       <c r="D273" s="3" t="inlineStr"/>
       <c r="E273" s="3" t="inlineStr">
         <is>
-          <t>長野県上田市別所温泉1853-3</t>
+          <t>長野県上田市別所温泉58</t>
         </is>
       </c>
       <c r="F273" s="3" t="inlineStr">
         <is>
-          <t>駅長</t>
+          <t>紺浴衣Ver</t>
         </is>
       </c>
       <c r="G273" s="3" t="inlineStr"/>
@@ -13788,7 +14313,7 @@
       </c>
       <c r="I273" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="J273" s="2" t="inlineStr"/>
@@ -13808,18 +14333,18 @@
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>しゅうぷろ</t>
+          <t>別所温泉駅観光案内所</t>
         </is>
       </c>
       <c r="D274" s="3" t="inlineStr"/>
       <c r="E274" s="3" t="inlineStr">
         <is>
-          <t>長野県上田市別所温泉１６６１</t>
+          <t>長野県上田市別所温泉1853-3</t>
         </is>
       </c>
       <c r="F274" s="3" t="inlineStr">
         <is>
-          <t>芸姑</t>
+          <t>駅長</t>
         </is>
       </c>
       <c r="G274" s="3" t="inlineStr"/>
@@ -13830,7 +14355,7 @@
       </c>
       <c r="I274" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="J274" s="2" t="inlineStr"/>
@@ -15321,7 +15846,7 @@
       <c r="G308" s="3" t="inlineStr"/>
       <c r="H308" s="2" t="inlineStr">
         <is>
-          <t>発売中</t>
+          <t>発売前</t>
         </is>
       </c>
       <c r="I308" s="2" t="inlineStr">
@@ -17913,7 +18438,7 @@
       <c r="G366" s="3" t="inlineStr"/>
       <c r="H366" s="2" t="inlineStr">
         <is>
-          <t>発売中</t>
+          <t>発売前</t>
         </is>
       </c>
       <c r="I366" s="2" t="inlineStr">
